--- a/topic00-induction/unit-1/talk-0/archive/timetable.xlsx
+++ b/topic00-induction/unit-1/talk-0/archive/timetable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maireadmeagher/Documents/GitRepos/prog-fund-1-sept-25/topic01-intro-to-module/unit-01a-introduction/talk-0/archive/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maireadmeagher/Documents/GitRepos/prog-fund-1-sept-25/topic00-induction/unit-1/talk-0/archive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33AB9668-3E49-7346-9C47-80E33A2347A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B31268A-9743-2143-A116-5F13863793A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1940" yWindow="2720" windowWidth="29140" windowHeight="17680" xr2:uid="{12B3B812-4830-C349-8EFE-A4D906CFA645}"/>
+    <workbookView xWindow="920" yWindow="940" windowWidth="29140" windowHeight="17680" xr2:uid="{12B3B812-4830-C349-8EFE-A4D906CFA645}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -75,12 +75,6 @@
   </si>
   <si>
     <t>W1
-2:15-3:15
-Lab 1
-IT118</t>
-  </si>
-  <si>
-    <t>W1
 10:15- 12:15
 Labs 2,3
 IT118</t>
@@ -130,6 +124,12 @@
   <si>
     <t>Programming Fundamentals Timetable for W3/4
 (Lectures and Practical Classes)</t>
+  </si>
+  <si>
+    <t>W1
+2:15-3:15
+Lab 1
+ITG18</t>
   </si>
 </sst>
 </file>
@@ -258,43 +258,43 @@
     <xf numFmtId="20" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -626,20 +626,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="64" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="I2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="I2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -684,7 +684,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -696,17 +696,17 @@
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="11" t="s">
-        <v>15</v>
+      <c r="M5" s="15" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="62" customHeight="1" x14ac:dyDescent="0.2">
@@ -714,12 +714,12 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="8"/>
+      <c r="E6" s="14"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
-      <c r="M6" s="12"/>
+      <c r="M6" s="16"/>
     </row>
     <row r="7" spans="1:13" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
@@ -731,15 +731,15 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
-      <c r="M7" s="16" t="s">
-        <v>16</v>
+      <c r="M7" s="7" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="1"/>
@@ -752,21 +752,21 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="6" t="s">
-        <v>9</v>
+      <c r="D9" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="E9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
-      <c r="L9" s="13" t="s">
-        <v>13</v>
+      <c r="L9" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="1:13" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
-        <v>17</v>
+      <c r="A10" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -775,13 +775,13 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
-      <c r="L10" s="14" t="s">
-        <v>14</v>
+      <c r="L10" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="10"/>
+      <c r="A11" s="11"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -789,7 +789,7 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
-      <c r="L11" s="15"/>
+      <c r="L11" s="9"/>
       <c r="M11" s="1"/>
     </row>
   </sheetData>

--- a/topic00-induction/unit-1/talk-0/archive/timetable.xlsx
+++ b/topic00-induction/unit-1/talk-0/archive/timetable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maireadmeagher/Documents/GitRepos/prog-fund-1-sept-25/topic00-induction/unit-1/talk-0/archive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B31268A-9743-2143-A116-5F13863793A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F7CB3CF-2336-E043-B691-4A7EB7A58B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="920" yWindow="940" windowWidth="29140" windowHeight="17680" xr2:uid="{12B3B812-4830-C349-8EFE-A4D906CFA645}"/>
+    <workbookView xWindow="920" yWindow="860" windowWidth="29140" windowHeight="17680" xr2:uid="{12B3B812-4830-C349-8EFE-A4D906CFA645}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -116,12 +116,6 @@
 IT1</t>
   </si>
   <si>
-    <t>W2
-3:15-4:15
-Labs 1,2
-IT222</t>
-  </si>
-  <si>
     <t>Programming Fundamentals Timetable for W3/4
 (Lectures and Practical Classes)</t>
   </si>
@@ -130,6 +124,12 @@
 2:15-3:15
 Lab 1
 ITG18</t>
+  </si>
+  <si>
+    <t>W2
+3:15-5:15
+Labs 1,2
+IT222</t>
   </si>
 </sst>
 </file>
@@ -152,7 +152,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -192,6 +192,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF27E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -249,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -297,6 +315,13 @@
     <xf numFmtId="20" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -618,188 +643,218 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D2D0417-CDFB-FE42-A251-CA59BBC86C91}">
-  <dimension ref="A2:M11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="5" width="12.83203125" customWidth="1"/>
-    <col min="9" max="13" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" customWidth="1"/>
+    <col min="8" max="12" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" ht="64" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G1" s="19"/>
+    </row>
+    <row r="2" spans="1:12" ht="64" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="12"/>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12"/>
-      <c r="I2" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="F2" s="12"/>
+      <c r="H2" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H3" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="I3" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="76" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="21">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="2"/>
       <c r="E4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="3" t="s">
+      <c r="F4" s="1"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" spans="1:13" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+    </row>
+    <row r="5" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="21">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="1"/>
+      <c r="F5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="15" t="s">
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
+    <row r="6" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="21">
+        <v>0.46875</v>
+      </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="14"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="16"/>
-    </row>
-    <row r="7" spans="1:13" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="14"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="16"/>
+    </row>
+    <row r="7" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="21">
+        <v>0.51041666666666663</v>
+      </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="7" t="s">
+      <c r="F7" s="1"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
+    <row r="8" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="21">
+        <v>5.2083333333333336E-2</v>
+      </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="1"/>
+      <c r="E8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="M8" s="1"/>
-    </row>
-    <row r="9" spans="1:13" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="18"/>
+    </row>
+    <row r="9" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="21">
+        <v>9.375E-2</v>
+      </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="1"/>
+      <c r="E9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L9" s="18"/>
+    </row>
+    <row r="10" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="21">
+        <v>0.13541666666666666</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M9" s="1"/>
-    </row>
-    <row r="10" spans="1:13" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="8" t="s">
+      <c r="F10" s="1"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="M10" s="1"/>
-    </row>
-    <row r="11" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="11"/>
-      <c r="B11" s="1"/>
+      <c r="L10" s="18"/>
+    </row>
+    <row r="11" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="21">
+        <v>0.17708333333333334</v>
+      </c>
+      <c r="B11" s="11"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="L5:L6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
